--- a/VerveStacks_GBR_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCC08507-5D85-47B6-A178-A2C7F728EE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C140E109-BA67-45D6-9796-55A93EB5458F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1013DA44-91FE-4B70-8F01-4F1D28291DDE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3ADC7A58-BD08-4A1B-9185-862027AB53F7}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -640,7 +640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD5BFBD-2B0A-459A-B295-3F458B504F36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4CFB26-4F7E-4964-B6E9-9AF7F361635D}">
   <dimension ref="B3:L28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
